--- a/RQ2_Prompt_Effectiveness_Modeling/results/qualitative/gate1/gate1_qualitative_patterns.xlsx
+++ b/RQ2_Prompt_Effectiveness_Modeling/results/qualitative/gate1/gate1_qualitative_patterns.xlsx
@@ -575,7 +575,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Kotlin の sksamuel/scrimage ライブラリで、画像上に文字列を描画し、文字列の縁取りをするコードを生成してください。文字の色は白、縁は黒で描画します。</t>
+          <t>Using Kotlin with the sksamuel/scrimage library, generate code to draw text on an image with an outline. Render white text with a black border.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>git diff は違いがあった場合のステータスコードは何でしょうか。ありがとうございます。diffはどうでしょうか。</t>
+          <t>What is the exit status code for git diff when differences are found? Thank you. Also, what about diff?</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">

--- a/RQ2_Prompt_Effectiveness_Modeling/results/qualitative/gate1/gate1_qualitative_patterns.xlsx
+++ b/RQ2_Prompt_Effectiveness_Modeling/results/qualitative/gate1/gate1_qualitative_patterns.xlsx
@@ -1025,7 +1025,7 @@
         <v>2</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>0</v>
@@ -1091,7 +1091,7 @@
         <v>1</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>0</v>
@@ -1157,7 +1157,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>0</v>
